--- a/src/test/fixtures/forms-responses-http/export.xlsx
+++ b/src/test/fixtures/forms-responses-http/export.xlsx
@@ -39,16 +39,16 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>Ta9315f36-000001</x:t>
+    <x:t>Tba6d336f-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
   </x:si>
   <x:si>
-    <x:t>Ta9315f36-000002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ta9315f36-000003</x:t>
+    <x:t>Tba6d336f-000002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tba6d336f-000003</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/src/test/fixtures/forms-responses-http/export.xlsx
+++ b/src/test/fixtures/forms-responses-http/export.xlsx
@@ -39,16 +39,16 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>Tba6d336f-000001</x:t>
+    <x:t>TCC44FCEB-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
   </x:si>
   <x:si>
-    <x:t>Tba6d336f-000002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tba6d336f-000003</x:t>
+    <x:t>TCC44FCEB-000002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCC44FCEB-000003</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/src/test/fixtures/forms-responses-http/export.xlsx
+++ b/src/test/fixtures/forms-responses-http/export.xlsx
@@ -39,16 +39,16 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TCC44FCEB-000001</x:t>
+    <x:t>T8806EE91-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
   </x:si>
   <x:si>
-    <x:t>TCC44FCEB-000002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCC44FCEB-000003</x:t>
+    <x:t>T8806EE91-000002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T8806EE91-000003</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/src/test/fixtures/forms-responses-http/export.xlsx
+++ b/src/test/fixtures/forms-responses-http/export.xlsx
@@ -39,16 +39,16 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T8806EE91-000001</x:t>
+    <x:t>TDFA48B69-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
   </x:si>
   <x:si>
-    <x:t>T8806EE91-000002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T8806EE91-000003</x:t>
+    <x:t>TDFA48B69-000002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TDFA48B69-000003</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/src/test/fixtures/forms-responses-http/export.xlsx
+++ b/src/test/fixtures/forms-responses-http/export.xlsx
@@ -39,16 +39,16 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TDFA48B69-000001</x:t>
+    <x:t>TC5DBD79F-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
   </x:si>
   <x:si>
-    <x:t>TDFA48B69-000002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TDFA48B69-000003</x:t>
+    <x:t>TC5DBD79F-000002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TC5DBD79F-000003</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/src/test/fixtures/forms-responses-http/export.xlsx
+++ b/src/test/fixtures/forms-responses-http/export.xlsx
@@ -39,16 +39,16 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TC5DBD79F-000001</x:t>
+    <x:t>TC6F3F3D3-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
   </x:si>
   <x:si>
-    <x:t>TC5DBD79F-000002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TC5DBD79F-000003</x:t>
+    <x:t>TC6F3F3D3-000002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TC6F3F3D3-000003</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/src/test/fixtures/forms-responses-http/export.xlsx
+++ b/src/test/fixtures/forms-responses-http/export.xlsx
@@ -39,16 +39,16 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TC6F3F3D3-000001</x:t>
+    <x:t>T883D85A3-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
   </x:si>
   <x:si>
-    <x:t>TC6F3F3D3-000002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TC6F3F3D3-000003</x:t>
+    <x:t>T883D85A3-000002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T883D85A3-000003</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/src/test/fixtures/forms-responses-http/export.xlsx
+++ b/src/test/fixtures/forms-responses-http/export.xlsx
@@ -39,16 +39,16 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T883D85A3-000001</x:t>
+    <x:t>T8DC029EE-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
   </x:si>
   <x:si>
-    <x:t>T883D85A3-000002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T883D85A3-000003</x:t>
+    <x:t>T8DC029EE-000002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T8DC029EE-000003</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/src/test/fixtures/forms-responses-http/export.xlsx
+++ b/src/test/fixtures/forms-responses-http/export.xlsx
@@ -39,16 +39,16 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T8DC029EE-000001</x:t>
+    <x:t>T05DF9709-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
   </x:si>
   <x:si>
-    <x:t>T8DC029EE-000002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T8DC029EE-000003</x:t>
+    <x:t>T05DF9709-000002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T05DF9709-000003</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/src/test/fixtures/forms-responses-http/export.xlsx
+++ b/src/test/fixtures/forms-responses-http/export.xlsx
@@ -39,16 +39,16 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T05DF9709-000001</x:t>
+    <x:t>T038ED02A-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
   </x:si>
   <x:si>
-    <x:t>T05DF9709-000002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T05DF9709-000003</x:t>
+    <x:t>T038ED02A-000002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T038ED02A-000003</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/src/test/fixtures/forms-responses-http/export.xlsx
+++ b/src/test/fixtures/forms-responses-http/export.xlsx
@@ -39,16 +39,16 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T038ED02A-000001</x:t>
+    <x:t>TECEACF3D-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
   </x:si>
   <x:si>
-    <x:t>T038ED02A-000002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T038ED02A-000003</x:t>
+    <x:t>TECEACF3D-000002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TECEACF3D-000003</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/src/test/fixtures/forms-responses-http/export.xlsx
+++ b/src/test/fixtures/forms-responses-http/export.xlsx
@@ -39,16 +39,16 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TECEACF3D-000001</x:t>
+    <x:t>T2933F44A-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
   </x:si>
   <x:si>
-    <x:t>TECEACF3D-000002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TECEACF3D-000003</x:t>
+    <x:t>T2933F44A-000002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T2933F44A-000003</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/src/test/fixtures/forms-responses-http/export.xlsx
+++ b/src/test/fixtures/forms-responses-http/export.xlsx
@@ -39,16 +39,16 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T2933F44A-000001</x:t>
+    <x:t>TDE1A8877-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
   </x:si>
   <x:si>
-    <x:t>T2933F44A-000002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T2933F44A-000003</x:t>
+    <x:t>TDE1A8877-000002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TDE1A8877-000003</x:t>
   </x:si>
 </x:sst>
 </file>
